--- a/data/origem_teste.xlsx
+++ b/data/origem_teste.xlsx
@@ -413,194 +413,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ID_CLIENTE</t>
+          <t>CODIGO</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>NOME_CLIENTE</t>
+          <t>VALOR_NOVO</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>IDADE</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>STATUS_SISTEMA</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>UF</t>
+          <t>DESC_ORIGEM</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Alice Silva</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>25</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SP</t>
+        <v>101</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Prod A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bruno Costa</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Inativo</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>RJ</t>
+        <v>102</v>
+      </c>
+      <c r="B3" t="n">
+        <v>750</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prod B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Carlos Dias</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Daniela Souza</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>28</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Eduardo Melo</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>35</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Fernanda Lima</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>29</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Gabriel Santos</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>41</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Inativo</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RS</t>
+        <v>103</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Prod C</t>
         </is>
       </c>
     </row>
